--- a/AAII_Financials/Quarterly/MTD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MTD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="92">
   <si>
     <t>MTD</t>
   </si>
@@ -656,543 +656,556 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1027300</v>
+      </c>
+      <c r="E8" s="3">
         <v>947100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1129700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1029700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>983200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>883700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1045100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>954500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>946800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>925900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>935000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>942500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>982100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>928700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1057700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>985800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>978400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>897800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1037200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>952000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>924400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>804400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>938000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>807400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>690700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>649200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>844000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>753900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>731400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>679500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>817900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>734800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>722000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>660800</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>778000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>698800</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>653700</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>594600</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>709700</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>650600</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>377100</v>
+      </c>
+      <c r="E9" s="3">
         <v>391300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>454300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>420200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>403300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>357900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>405800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>382100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>381100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>377800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>383400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>382900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>398600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>382200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>425500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>401200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>406700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>378200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>430100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>396100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>387400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>332700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>378900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>337700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>292700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>274800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>345700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>318800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>311800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>291100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>340400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>315600</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>309400</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>285900</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>322300</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>297800</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>278700</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>251200</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>291100</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>281100</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>650200</v>
+      </c>
+      <c r="E10" s="3">
         <v>555800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>675400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>609500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>579900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>525900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>639300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>572500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>565700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>548100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>551600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>559500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>583500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>546600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>632200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>584600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>571700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>519600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>607100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>555900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>537000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>471700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>559100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>469700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>398000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>374400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>498300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>435100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>419600</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>388400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>477500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>419200</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>412600</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>374900</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>455700</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>401000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>375000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>343400</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>418600</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>369500</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1235,130 +1248,134 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>53000</v>
+      </c>
+      <c r="E12" s="3">
         <v>51300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>52600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>51100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>49300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>46300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>50100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>47100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>45800</v>
-      </c>
-      <c r="L12" s="3">
-        <v>46400</v>
       </c>
       <c r="M12" s="3">
         <v>46400</v>
       </c>
       <c r="N12" s="3">
+        <v>46400</v>
+      </c>
+      <c r="O12" s="3">
         <v>46100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>47200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>45500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>45900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>44100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>44000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>43000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>45600</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>42300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>42600</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>39300</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>39900</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>34700</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>31200</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>34400</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>35300</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>36000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>36600</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>36100</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>36200</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>34800</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>35300</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>34700</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>32300</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>32200</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>32900</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>31200</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>30200</v>
       </c>
-      <c r="AP12" s="3">
+      <c r="AQ12" s="3">
         <v>30100</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1479,150 +1496,156 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>13900</v>
+      </c>
+      <c r="E14" s="3">
         <v>7300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>7300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>3600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>3800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>5300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>9700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>13100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>7400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>8000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>4300</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>2000</v>
       </c>
       <c r="R14" s="3">
         <v>2000</v>
       </c>
       <c r="S14" s="3">
+        <v>2000</v>
+      </c>
+      <c r="T14" s="3">
         <v>2300</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>4500</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>3100</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>700</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>900</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>4000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>3200</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>4600</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>900</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>1900</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>4600</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>6700</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>2900</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>1500</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>-11200</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>2200</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>7300</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>4400</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>3900</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>8500</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>4000</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>1400</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>1700</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>9700</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>19400</v>
+      </c>
+      <c r="E15" s="3">
         <v>19600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>19700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>20000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>17600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>17200</v>
-      </c>
-      <c r="I15" s="3">
-        <v>18200</v>
       </c>
       <c r="J15" s="3">
         <v>18200</v>
@@ -1634,97 +1657,100 @@
         <v>18200</v>
       </c>
       <c r="M15" s="3">
+        <v>18200</v>
+      </c>
+      <c r="N15" s="3">
         <v>18100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>18300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>18000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>17800</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>16500</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>16700</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>16400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>16600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>16900</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>16000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>16200</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>13900</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>14700</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>14100</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>13900</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>14000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>12800</v>
-      </c>
-      <c r="AD15" s="3">
-        <v>12300</v>
       </c>
       <c r="AE15" s="3">
         <v>12300</v>
       </c>
       <c r="AF15" s="3">
+        <v>12300</v>
+      </c>
+      <c r="AG15" s="3">
         <v>12200</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>12000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>11900</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>12000</v>
-      </c>
-      <c r="AJ15" s="3">
-        <v>11700</v>
       </c>
       <c r="AK15" s="3">
         <v>11700</v>
       </c>
       <c r="AL15" s="3">
+        <v>11700</v>
+      </c>
+      <c r="AM15" s="3">
         <v>10700</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>10200</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>10000</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>9900</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>9100</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,252 +1790,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>706800</v>
+      </c>
+      <c r="E17" s="3">
         <v>726500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>782800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>736300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>714100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>667300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>709400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>674300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>679000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>674800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>669200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>663000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>690600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>678300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>732700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>710000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>721700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>684800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>751300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>704400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>694000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>619000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>668800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>601500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>535400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>530700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>612800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>584500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>576200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>553800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>587500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>574500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>578400</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>543400</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>584100</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>559200</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>526800</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>480700</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>528400</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>517300</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>320500</v>
+      </c>
+      <c r="E18" s="3">
         <v>220600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>346900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>293400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>269100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>216400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>335700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>280300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>267700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>251100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>265800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>279500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>291500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>250500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>325000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>275800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>256700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>213000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>285900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>247600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>230400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>185400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>269200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>205900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>155300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>118500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>231200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>169400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>155300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>125700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>230400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>160300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>143600</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>117400</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>193900</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>139600</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>126900</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>113900</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>181300</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>133300</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -2052,53 +2085,54 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
         <v>-13300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-5900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1400</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
@@ -2174,175 +2208,181 @@
       <c r="AP20" s="3">
         <v>0</v>
       </c>
+      <c r="AQ20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>339900</v>
+      </c>
+      <c r="E21" s="3">
         <v>253500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>367200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>314200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>286600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>239600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>353100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>298400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>285600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>267700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>283300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>297100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>308700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>266800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>353300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>304300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>284500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>241500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>314500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>274800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>257900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>210200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>294900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>230600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>179300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>142600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>253600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>191600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>177200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>147700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>251700</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>181500</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>165000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>138300</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>214600</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>158800</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>145000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>131900</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>199400</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>150800</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>17200</v>
+      </c>
+      <c r="E22" s="3">
         <v>17000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>17400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>17700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>16800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>16700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>17900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>18600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>19000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>19200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>19700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>20300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>19200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>18200</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
       <c r="R22" s="3">
         <v>0</v>
       </c>
@@ -2418,252 +2458,261 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>289400</v>
+      </c>
+      <c r="E23" s="3">
         <v>209700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>329100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>269200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>248700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>201900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>314500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>259000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>243200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>220500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>232600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>251200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>263400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>226600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>325000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>275900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>256700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>213000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>286000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>247600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>230400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>185400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>269200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>205800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>155300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>118500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>231100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>169400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>155200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>125700</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>230500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>160400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>143600</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>117400</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>193900</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>139600</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>126800</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>113800</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>181300</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>133300</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>56500</v>
+      </c>
+      <c r="E24" s="3">
         <v>40200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>43300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>51700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>46300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>38400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>62200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>47400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>21400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>43000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>47800</v>
-      </c>
-      <c r="N24" s="3">
-        <v>49500</v>
       </c>
       <c r="O24" s="3">
         <v>49500</v>
       </c>
       <c r="P24" s="3">
+        <v>49500</v>
+      </c>
+      <c r="Q24" s="3">
         <v>38200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>59200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>55300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>44600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>39000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>55100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>43900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>45600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>35800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>52900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>44000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>28700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>20400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>38400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>40000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>28100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>13900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>45700</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>33700</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>32100</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>24100</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>44900</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>34700</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>25300</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>21400</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>43500</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>32000</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2784,252 +2833,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>232900</v>
+      </c>
+      <c r="E26" s="3">
         <v>169500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>285800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>217500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>202300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>163600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>252300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>211500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>221800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>177500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>184800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>201600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>213900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>188400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>265800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>220600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>212100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>174000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>230900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>203700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>184800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>149700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>216300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>161800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>126600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>98100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>192700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>129400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>127200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>111800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>184800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>126700</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>111500</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>93300</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>149000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>105000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>101600</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>92500</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>137800</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>101300</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>232900</v>
+      </c>
+      <c r="E27" s="3">
         <v>169500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>285800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>217500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>202300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>163600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>252300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>211500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>221800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>177500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>184800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>201600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>213900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>188400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>265800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>220600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>212100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>174000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>230900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>203700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>184800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>149700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>216300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>161800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>126600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>98100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>192700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>129400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>127200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>111800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>184800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>126700</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>111500</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>93300</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>149000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>105000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>101600</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>92500</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>137800</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>101300</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -3224,8 +3285,8 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>24</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>24</v>
@@ -3242,11 +3303,11 @@
       <c r="AF29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-3600</v>
-      </c>
-      <c r="AH29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>24</v>
@@ -3254,11 +3315,11 @@
       <c r="AJ29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AL29" s="3">
         <v>-72000</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>24</v>
@@ -3272,8 +3333,11 @@
       <c r="AP29" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,53 +3583,56 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
         <v>13300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>5900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
@@ -3638,130 +3708,136 @@
       <c r="AP32" s="3">
         <v>0</v>
       </c>
+      <c r="AQ32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>232900</v>
+      </c>
+      <c r="E33" s="3">
         <v>169500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>285800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>217500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>202300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>163600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>252300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>211500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>221800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>177500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>184800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>201600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>213900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>188400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>265800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>220600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>212100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>174000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>230900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>203700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>184800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>149700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>216300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>161800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>126600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>98100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>192700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>129400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>127200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>111800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>181200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>126700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>111500</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>93300</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>77000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>105000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>101600</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>92500</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>137800</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>101300</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,257 +3958,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>232900</v>
+      </c>
+      <c r="E35" s="3">
         <v>169500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>285800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>217500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>202300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>163600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>252300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>211500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>221800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>177500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>184800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>201600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>213900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>188400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>265800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>220600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>212100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>174000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>230900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>203700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>184800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>149700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>216300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>161800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>126600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>98100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>192700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>129400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>127200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>111800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>181200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>126700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>111500</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>93300</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>77000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>105000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>101600</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>92500</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>137800</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>101300</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,130 +4305,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>51400</v>
+      </c>
+      <c r="E41" s="3">
         <v>60600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>66900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>69100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>61800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>64300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>59400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>71600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>70800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>70200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>69800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>69700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>83600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>89100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>96000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>122100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>109400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>116900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>98600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>183700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>142300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>106700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>94300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>153700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>127300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>323600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>207800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>120500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>124400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>126500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>178100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>137400</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>183200</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>98900</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>148700</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>169100</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>146300</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>164900</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>158700</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>146100</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4463,496 +4553,511 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>741000</v>
+      </c>
+      <c r="E43" s="3">
         <v>708200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>778200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>687300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>681600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>638400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>687100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>637200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>634700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>650300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>663900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>635000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>648000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>640100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>709300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>611400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>626600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>617900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>647300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>603400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>600200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>574400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>593800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>521800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>490400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>518600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>566300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>503200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>498700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>489300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>535500</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>494900</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>486200</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>483900</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>528600</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>483200</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>448100</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>439400</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>455000</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>414600</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>411600</v>
+      </c>
+      <c r="E44" s="3">
         <v>404800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>387200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>401800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>388100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>358800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>342300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>375800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>366400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>373700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>385900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>376000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>395000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>427500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>441700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>451300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>463300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>446500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>414500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>381500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>350200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>321300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>297600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>292300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>299700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>292100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>274300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>281000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>286300</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>282100</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>268800</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>277300</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>270000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>278300</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>255400</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>263500</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>253700</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>242400</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>222000</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>240000</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>143500</v>
+      </c>
+      <c r="E45" s="3">
         <v>158300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>130300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>123100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>113000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>103300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>105200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>113600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>106400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>116900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>110600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>116300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>120000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>130100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>128100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>131000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>125300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>128600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>108900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>77700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>80000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>77800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>71200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>78500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>72400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>66600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>61300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>59000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>71900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>71500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>63400</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>61900</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>63900</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>66200</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>74000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>70800</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>65600</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>66200</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>61100</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>145400</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1347400</v>
+      </c>
+      <c r="E46" s="3">
         <v>1331900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1362700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1281200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1244500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1164800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1193900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1198200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1178300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1211100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1230200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1196900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1246500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1286800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1375100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1315900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1324700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1309900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1269400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1246200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1172600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1080200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1056900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1046300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>989800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1200900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1109600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>963800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>981400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>969400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1045900</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>971500</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>1003300</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>927400</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>1006700</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>986600</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>913800</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>912900</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>896800</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>946100</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4995,8 +5100,8 @@
       <c r="P47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -5073,252 +5178,261 @@
       <c r="AP47" s="3">
         <v>0</v>
       </c>
+      <c r="AQ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>831900</v>
+      </c>
+      <c r="E48" s="3">
         <v>830300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>973000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>817700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>817400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>778000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>883000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>790400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>768700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>773500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>917800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>763200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>780700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>780000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>778600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>728600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>760900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>787500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>799400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>783800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>790500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>780200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>798900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>758000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>743400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>742700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>836000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>810800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>816200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>809500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>717500</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>697700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>678700</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>696900</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>668300</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>641700</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>600900</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>572100</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>563700</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>527500</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1001500</v>
+      </c>
+      <c r="E49" s="3">
         <v>1010600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1018100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1009600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>937700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>925000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>926100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>934900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>933500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>940200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>955500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>947800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>959700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>961900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>966200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>933500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>941800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>955200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>956100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>927800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>935900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>939300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>747100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>740900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>739800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>742600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>742200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>740600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>745800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>749500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>752100</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>758800</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>756300</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>769500</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>766600</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>768400</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>647900</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>644100</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>643400</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>651300</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,130 +5678,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>448900</v>
+      </c>
+      <c r="E52" s="3">
         <v>454200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>317500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>376800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>363800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>331200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>202400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>364500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>338100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>326800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>220900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>353100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>355600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>353100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>372500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>316400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>309100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>303600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>302000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>249300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>243900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>228700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>211700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>221300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>206700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>199700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>101500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>120700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>117500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>108300</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>103400</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>129700</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>119900</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>118100</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>108300</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>100500</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>85400</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>74700</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>62900</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>96100</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3670900</v>
+      </c>
+      <c r="E54" s="3">
         <v>3668900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3712600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3521500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3400500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3234700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3240000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3319800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3249200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3283100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3355600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3288700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3370400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3409900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>3492400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>3294500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>3336400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>3356200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>3326800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>3207200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>3142900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>3028400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2814500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2766500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2679600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>2885800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>2789300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>2635900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>2660900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>2636700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>2618800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>2557700</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>2558200</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>2511900</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>2549800</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>2497200</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>2248000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>2203800</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>2166800</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>2221000</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,740 +6145,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>229800</v>
+      </c>
+      <c r="E57" s="3">
         <v>228700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>266600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>247400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>216200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>201400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>215800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>202900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>199500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>189400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>210400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>174000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>170200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>176700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>252500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>226700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>267500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>259400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>272900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>219300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>210800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>189300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>175800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>146600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>155900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>168500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>185600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>148200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>160600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>174600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>196600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>156400</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>170900</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>164600</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>167600</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>148500</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>143600</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>137800</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>146600</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>129700</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>92100</v>
+      </c>
+      <c r="E58" s="3">
         <v>67000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>99000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>63600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>60200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>182900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>211700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>185800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>311200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>183200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>220700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>179100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>107400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>107100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>106100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>153600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>106600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>105300</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>101100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>53500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>53000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>52500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>50300</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>55100</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>53600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>56400</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>55900</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>48600</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>51900</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>53800</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>49700</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>55800</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>52100</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>14900</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>19700</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>18500</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>21600</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>19500</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>19000</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>21800</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>277300</v>
+        <v>448800</v>
       </c>
       <c r="E59" s="3">
+        <v>438800</v>
+      </c>
+      <c r="F59" s="3">
         <v>450100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>503300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>488300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>453500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>401600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>436100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>434100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>445400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>432900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>404100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>421500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>406800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>789100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>784600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>744500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>722800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>772500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>728700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>674500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>600000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>614200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>562300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>493300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>454900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>513100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>522500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>494700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>479500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>488100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>485300</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>465900</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>457400</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>502400</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>485300</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>423600</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>403900</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>421900</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>469400</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1200500</v>
+      </c>
+      <c r="E60" s="3">
         <v>1108400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1198100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1192100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1106900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1149700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1168200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1185000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1281200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1131900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1181100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1070400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1008000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1004200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1147700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1164900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1118600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1087400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1146500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1001600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>938400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>841800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>840300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>764100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>702800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>679800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>754500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>719300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>707300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>708000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>734400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>697500</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>688800</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>636900</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>689700</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>652400</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>588800</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>561200</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>587500</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>620800</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2045300</v>
+      </c>
+      <c r="E61" s="3">
         <v>2161600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2166300</v>
       </c>
-      <c r="F61" s="3">
-        <v>2178300</v>
-      </c>
       <c r="G61" s="3">
+        <v>2146200</v>
+      </c>
+      <c r="H61" s="3">
         <v>2123700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1891200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1913200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1891700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1746600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1903600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1975600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1929400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2045500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2015800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1908500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1825300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1821500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1766800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1580800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1639600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1602000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1561100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1284200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1169100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1146600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1513000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1235400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1124300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1087900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1008500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>985000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>988900</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1020400</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>978700</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>960200</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>1050700</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>947800</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>944200</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>875100</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>826000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>266800</v>
+      </c>
+      <c r="E62" s="3">
         <v>293500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>220100</v>
       </c>
-      <c r="F62" s="3">
-        <v>292200</v>
-      </c>
       <c r="G62" s="3">
+        <v>324300</v>
+      </c>
+      <c r="H62" s="3">
         <v>313500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>271900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>181500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>289800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>272400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>306200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>240200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>282600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>290600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>301000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>411400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>387100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>389100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>417400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>428000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>406800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>411100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>422900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>407400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>390300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>380100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>386500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>378700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>354000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>361600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>358500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>309300</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>339700</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>316500</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>335600</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>352700</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>281200</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>249400</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>258500</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>269300</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>273600</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3658100</v>
+      </c>
+      <c r="E66" s="3">
         <v>3710800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3736300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3770700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3659300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3416700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3366900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3474200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3401900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3441800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3505500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3394600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3460100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3434400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3467600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3377300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3329200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3271600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3155400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3048000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2951500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2825700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2531900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2323500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2229600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2579400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2368500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2197600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>2156800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>2074900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>2028800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>2026000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>2025800</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>1951200</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>2002500</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>1984200</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>1786000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>1763900</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>1731800</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>1720500</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,130 +7938,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>9640300</v>
+      </c>
+      <c r="E72" s="3">
         <v>9407600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>9238200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>8954800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>8737300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>8535000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>8371400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>8121400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7909900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>7688100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>7510800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>7328300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>7126700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>6912800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>6726900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>6463300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>6242900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>6030900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>5859300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>5632000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>5429100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>5244400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>5095600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>4882300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>4720500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>4595200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>4499300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>4309700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>4180300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>4053700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>3941900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>3763900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>3637600</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>3526400</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>3433300</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>3360300</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>3256700</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>3157300</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>3065700</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>2934200</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>12800</v>
+      </c>
+      <c r="E76" s="3">
         <v>-41900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-23600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-249200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-258800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-182000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-126900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-154400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-152800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-158700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-149900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-105900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-89700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-24500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>24800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-82800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>7300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>84600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>171400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>159200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>191400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>202600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>282700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>443100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>450100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>306400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>420800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>438300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>504100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>561800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>590100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>531600</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>532400</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>560700</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>547300</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>513000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>461900</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>439900</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>434900</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>500500</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,257 +8688,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>232900</v>
+      </c>
+      <c r="E81" s="3">
         <v>169500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>285800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>217500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>202300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>163600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>252300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>211500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>221800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>177500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>184800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>201600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>213900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>188400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>265800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>220600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>212100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>174000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>230900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>203700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>184800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>149700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>216300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>161800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>126600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>98100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>192700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>129400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>127200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>111800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>181200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>126700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>111500</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>93300</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>77000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>105000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>101600</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>92500</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>137800</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>101300</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,130 +8990,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>12900</v>
+      </c>
+      <c r="E83" s="3">
         <v>12500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>12600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>12800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>12400</v>
-      </c>
-      <c r="H83" s="3">
-        <v>12500</v>
       </c>
       <c r="I83" s="3">
         <v>12500</v>
       </c>
       <c r="J83" s="3">
-        <v>12200</v>
+        <v>12500</v>
       </c>
       <c r="K83" s="3">
         <v>12200</v>
       </c>
       <c r="L83" s="3">
+        <v>12200</v>
+      </c>
+      <c r="M83" s="3">
         <v>12000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>11800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>11700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>11400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>11900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>28300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>28400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>27800</v>
-      </c>
-      <c r="T83" s="3">
-        <v>28500</v>
       </c>
       <c r="U83" s="3">
         <v>28500</v>
       </c>
       <c r="V83" s="3">
+        <v>28500</v>
+      </c>
+      <c r="W83" s="3">
         <v>27200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>27500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>24800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>25800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>24700</v>
-      </c>
-      <c r="AA83" s="3">
-        <v>24100</v>
       </c>
       <c r="AB83" s="3">
         <v>24100</v>
       </c>
       <c r="AC83" s="3">
+        <v>24100</v>
+      </c>
+      <c r="AD83" s="3">
         <v>22500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>22300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>21900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>22000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>21200</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>21100</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>21400</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>20900</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>20700</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>19200</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>18200</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>18000</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>18100</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>17500</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>310400</v>
+      </c>
+      <c r="E89" s="3">
         <v>139800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>225600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>299400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>236400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>194400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>266200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>254700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>257500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>190000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>281500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>264300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>266800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>153300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>303600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>245400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>219200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>90800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>241100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>263300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>245500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>158900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>250900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>225100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>183200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>65500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>201700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>175900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>127100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>98800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>198600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>149700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>140200</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>76600</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>165100</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>145900</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>137800</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>67600</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>153400</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>156100</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,130 +9910,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-27800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-17400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-41500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-24500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-23900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-17300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-41300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-21400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-23800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-17400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-32400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-21000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-28800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-23200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-32000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-26800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-43200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-19200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-37800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-22400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-22800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-24600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-35100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-20300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-18300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-18800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-25700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-26900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-22300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-22400</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-46100</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-35100</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-31800</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-29800</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-41600</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-37300</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-27500</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-21000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-145400</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-73600</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-31300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-40400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-98900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-47700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-6900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-51100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-37600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-21800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-8900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-35500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-30900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-42900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-22400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-50000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-48700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-33500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-7100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-62900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-25200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-34600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-191500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-30300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-19500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-16100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-34500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-22600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-31300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-27700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-17500</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-44300</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-44100</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-28100</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-22500</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-37200</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-140100</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-29400</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-10700</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-72900</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-126600</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,8 +10455,9 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10266,8 +10500,8 @@
       <c r="P96" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -10344,8 +10578,11 @@
       <c r="AP96" s="3">
         <v>0</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,370 +10953,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-317700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-114300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-192100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-192900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-186000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-184100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-223700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-218900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-234300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-179100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-249000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-245600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-227400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-137600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-285400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-177300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-188800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-64500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-264200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-195700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-177300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>46700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-286500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-182400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-362400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>87300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-95200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-145300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-100700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-136200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-113500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-146000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-20800</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-107700</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-152300</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>15200</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-128500</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-53900</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-61700</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>18400</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="E101" s="3">
         <v>1500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-3700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>2600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>3100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-2000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>5700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-6800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-4300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>5700</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-6800</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-4300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-900</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>900</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-1000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>1900</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>6500</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>3100</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-1100</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-2500</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>3300</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-3200</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-700</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>3300</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-100</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-5300</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-7100</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>3800</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>4000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>1800</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>1500</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>3300</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-5800</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-6300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>7200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>4900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-12200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-13900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-5500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-6900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-26200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>12700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-7500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>18400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-85100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>41400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>35600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>12400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-59400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>26400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-196300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>115800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>87300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-3900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-2000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-51600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>40700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-45700</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>84200</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-49700</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-20400</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>22800</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-18600</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>6200</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>12500</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>31500</v>
       </c>
     </row>
